--- a/models/comb_test/20261022-003918/comb_test_results.xlsx
+++ b/models/comb_test/20261022-003918/comb_test_results.xlsx
@@ -9,12 +9,14 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ML_all_models" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ML_best_vote_per_setup" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ML_nested_check" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NN_all_configs" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NN_window_length" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NN_finalists" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Confusion" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ML_marginals" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ML_person_spread" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ML_best_vote_per_setup" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ML_nested_check" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NN_all_configs" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NN_window_length" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NN_finalists" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Confusion" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -708,6 +710,407 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ML winner (rows = truth, % of row)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>FIST</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>THUMB_UP</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>WAVE_LEFT</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>WAVE_RIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FIST</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="C4" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>93</v>
+      </c>
+      <c r="E5" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>THUMB_UP</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>WAVE_LEFT</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>WAVE_RIGHT</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G8" t="n">
+        <v>91.59999999999999</v>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NN winner gru-w0.7-h32-d0.25-lr0.003-s0 (rows = truth, % of row)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>FIST</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>THUMB_UP</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>WAVE_LEFT</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>WAVE_RIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FIST</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="C11" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="C12" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D13" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>THUMB_UP</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="C14" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="E14" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>WAVE_LEFT</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="G15" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>WAVE_RIGHT</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C16" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G16" t="n">
+        <v>85.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -37532,6 +37935,614 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>choice</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>fits</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>best_%</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>mean_%</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>worst_%</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>representation</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>bandpass</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>192</v>
+      </c>
+      <c r="D2" t="n">
+        <v>77.36</v>
+      </c>
+      <c r="E2" t="n">
+        <v>63.26</v>
+      </c>
+      <c r="F2" t="n">
+        <v>54.1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>representation</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>192</v>
+      </c>
+      <c r="D3" t="n">
+        <v>76.88</v>
+      </c>
+      <c r="E3" t="n">
+        <v>64.54000000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>56.45</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>representation</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>envelope</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>192</v>
+      </c>
+      <c r="D4" t="n">
+        <v>64.02</v>
+      </c>
+      <c r="E4" t="n">
+        <v>57.27</v>
+      </c>
+      <c r="F4" t="n">
+        <v>49.52</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>feature set</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>192</v>
+      </c>
+      <c r="D5" t="n">
+        <v>77.36</v>
+      </c>
+      <c r="E5" t="n">
+        <v>63.16</v>
+      </c>
+      <c r="F5" t="n">
+        <v>49.52</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>feature set</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>192</v>
+      </c>
+      <c r="D6" t="n">
+        <v>74.44</v>
+      </c>
+      <c r="E6" t="n">
+        <v>62.86</v>
+      </c>
+      <c r="F6" t="n">
+        <v>54.71</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>feature set</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>classic</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>192</v>
+      </c>
+      <c r="D7" t="n">
+        <v>66.02</v>
+      </c>
+      <c r="E7" t="n">
+        <v>59.05</v>
+      </c>
+      <c r="F7" t="n">
+        <v>54.1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>window length (s)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>144</v>
+      </c>
+      <c r="D8" t="n">
+        <v>77.36</v>
+      </c>
+      <c r="E8" t="n">
+        <v>62.22</v>
+      </c>
+      <c r="F8" t="n">
+        <v>50.13</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>window length (s)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>144</v>
+      </c>
+      <c r="D9" t="n">
+        <v>76.84999999999999</v>
+      </c>
+      <c r="E9" t="n">
+        <v>62</v>
+      </c>
+      <c r="F9" t="n">
+        <v>49.52</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>window length (s)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>144</v>
+      </c>
+      <c r="D10" t="n">
+        <v>75.55</v>
+      </c>
+      <c r="E10" t="n">
+        <v>62.34</v>
+      </c>
+      <c r="F10" t="n">
+        <v>53.21</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>window length (s)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>144</v>
+      </c>
+      <c r="D11" t="n">
+        <v>71.17</v>
+      </c>
+      <c r="E11" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>53.38</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>model family</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>extra_trees</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>72</v>
+      </c>
+      <c r="D12" t="n">
+        <v>77.36</v>
+      </c>
+      <c r="E12" t="n">
+        <v>64.48999999999999</v>
+      </c>
+      <c r="F12" t="n">
+        <v>55.27</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>model family</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>random_forest</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>72</v>
+      </c>
+      <c r="D13" t="n">
+        <v>76.88</v>
+      </c>
+      <c r="E13" t="n">
+        <v>64.28</v>
+      </c>
+      <c r="F13" t="n">
+        <v>55.02</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>model family</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>hist_gradient_boost</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>36</v>
+      </c>
+      <c r="D14" t="n">
+        <v>74.19</v>
+      </c>
+      <c r="E14" t="n">
+        <v>62.56</v>
+      </c>
+      <c r="F14" t="n">
+        <v>53.64</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>model family</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>knn</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>72</v>
+      </c>
+      <c r="D15" t="n">
+        <v>68.41</v>
+      </c>
+      <c r="E15" t="n">
+        <v>62.13</v>
+      </c>
+      <c r="F15" t="n">
+        <v>54.1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>model family</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>mlp</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>72</v>
+      </c>
+      <c r="D16" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="E16" t="n">
+        <v>62.07</v>
+      </c>
+      <c r="F16" t="n">
+        <v>54.07</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>model family</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>svm_rbf</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>144</v>
+      </c>
+      <c r="D17" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="E17" t="n">
+        <v>59.64</v>
+      </c>
+      <c r="F17" t="n">
+        <v>49.52</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>model family</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>logreg</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>72</v>
+      </c>
+      <c r="D18" t="n">
+        <v>64.09</v>
+      </c>
+      <c r="E18" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>53.78</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>model family</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>36</v>
+      </c>
+      <c r="D19" t="n">
+        <v>63.85</v>
+      </c>
+      <c r="E19" t="n">
+        <v>59.79</v>
+      </c>
+      <c r="F19" t="n">
+        <v>53.52</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>held-out person</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>best fit_%</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>median fit_%</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>worst fit_%</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Barbora</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>56.07</v>
+      </c>
+      <c r="C2" t="n">
+        <v>41.62</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.83</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Betka</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>88.43000000000001</v>
+      </c>
+      <c r="C3" t="n">
+        <v>64.15000000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>50.46</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Bruno</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>82.72</v>
+      </c>
+      <c r="C4" t="n">
+        <v>68.55</v>
+      </c>
+      <c r="D4" t="n">
+        <v>56.1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Dano</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>94.97</v>
+      </c>
+      <c r="C5" t="n">
+        <v>70.01000000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>58.76</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Miso</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>90.17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>59.12</v>
+      </c>
+      <c r="D6" t="n">
+        <v>39.64</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -39128,7 +40139,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -39270,7 +40281,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -40056,7 +41067,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -40158,7 +41169,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -40225,405 +41236,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr"/>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ML winner (rows = truth, % of row)</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>FIST</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>THUMB_UP</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>WAVE_LEFT</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>WAVE_RIGHT</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>FIST</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>68.3</v>
-      </c>
-      <c r="C3" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="C4" t="n">
-        <v>59.7</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>17.3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>93</v>
-      </c>
-      <c r="E5" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>THUMB_UP</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="C6" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>59.2</v>
-      </c>
-      <c r="F6" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>WAVE_LEFT</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>98.40000000000001</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>WAVE_RIGHT</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="C8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G8" t="n">
-        <v>91.59999999999999</v>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>NN winner gru-w0.7-h32-d0.25-lr0.003-s0 (rows = truth, % of row)</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>FIST</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>THUMB_UP</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>WAVE_LEFT</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>WAVE_RIGHT</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>FIST</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>48.7</v>
-      </c>
-      <c r="C11" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="C12" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E12" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>4.7</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D13" t="n">
-        <v>92.5</v>
-      </c>
-      <c r="E13" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>THUMB_UP</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="C14" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="D14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="E14" t="n">
-        <v>54.2</v>
-      </c>
-      <c r="F14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>WAVE_LEFT</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>93.3</v>
-      </c>
-      <c r="G15" t="n">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>WAVE_RIGHT</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="C16" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G16" t="n">
-        <v>85.2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>